--- a/DSlec/kakei2000.xlsx
+++ b/DSlec/kakei2000.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" mc:Ignorable="x15 xr xr6 xr10">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10808"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yamamoto/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yamamoto/R/bookdown/datalecture/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:40009_{D02A7132-437F-DB46-9527-07534B2AE282}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B0E157F-F90A-2545-A0FD-4991723F4C18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="11440" yWindow="5400" windowWidth="28300" windowHeight="17440"/>
+    <workbookView xWindow="7540" yWindow="3520" windowWidth="28300" windowHeight="17440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="h-year-a" sheetId="1" r:id="rId1"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="142">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="163">
   <si>
     <t>2000年</t>
   </si>
@@ -447,12 +447,77 @@
   </si>
   <si>
     <t>仕送り金</t>
+  </si>
+  <si>
+    <t>FY2000</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>FY2001</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>FY2002</t>
+  </si>
+  <si>
+    <t>FY2003</t>
+  </si>
+  <si>
+    <t>FY2004</t>
+  </si>
+  <si>
+    <t>FY2005</t>
+  </si>
+  <si>
+    <t>FY2006</t>
+  </si>
+  <si>
+    <t>FY2007</t>
+  </si>
+  <si>
+    <t>FY2008</t>
+  </si>
+  <si>
+    <t>FY2009</t>
+  </si>
+  <si>
+    <t>FY2010</t>
+  </si>
+  <si>
+    <t>FY2011</t>
+  </si>
+  <si>
+    <t>FY2012</t>
+  </si>
+  <si>
+    <t>FY2013</t>
+  </si>
+  <si>
+    <t>FY2014</t>
+  </si>
+  <si>
+    <t>FY2015</t>
+  </si>
+  <si>
+    <t>FY2016</t>
+  </si>
+  <si>
+    <t>FY2017</t>
+  </si>
+  <si>
+    <t>FY2018</t>
+  </si>
+  <si>
+    <t>FY2019</t>
+  </si>
+  <si>
+    <t>FY2020</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="19">
     <font>
       <sz val="12"/>
@@ -1397,7 +1462,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:AA85"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <cols>
@@ -1424,67 +1489,67 @@
         <v>26</v>
       </c>
       <c r="G1" t="s">
-        <v>0</v>
+        <v>142</v>
       </c>
       <c r="H1" t="s">
-        <v>1</v>
+        <v>143</v>
       </c>
       <c r="I1" t="s">
-        <v>2</v>
+        <v>144</v>
       </c>
       <c r="J1" t="s">
-        <v>3</v>
+        <v>145</v>
       </c>
       <c r="K1" t="s">
-        <v>4</v>
+        <v>146</v>
       </c>
       <c r="L1" t="s">
-        <v>5</v>
+        <v>147</v>
       </c>
       <c r="M1" t="s">
-        <v>6</v>
+        <v>148</v>
       </c>
       <c r="N1" t="s">
-        <v>7</v>
+        <v>149</v>
       </c>
       <c r="O1" t="s">
-        <v>8</v>
+        <v>150</v>
       </c>
       <c r="P1" t="s">
-        <v>9</v>
+        <v>151</v>
       </c>
       <c r="Q1" t="s">
-        <v>10</v>
+        <v>152</v>
       </c>
       <c r="R1" t="s">
-        <v>11</v>
+        <v>153</v>
       </c>
       <c r="S1" t="s">
-        <v>12</v>
+        <v>154</v>
       </c>
       <c r="T1" t="s">
-        <v>13</v>
+        <v>155</v>
       </c>
       <c r="U1" t="s">
-        <v>14</v>
+        <v>156</v>
       </c>
       <c r="V1" t="s">
-        <v>15</v>
+        <v>157</v>
       </c>
       <c r="W1" t="s">
-        <v>16</v>
+        <v>158</v>
       </c>
       <c r="X1" t="s">
-        <v>17</v>
+        <v>159</v>
       </c>
       <c r="Y1" t="s">
-        <v>18</v>
+        <v>160</v>
       </c>
       <c r="Z1" t="s">
-        <v>19</v>
+        <v>161</v>
       </c>
       <c r="AA1" t="s">
-        <v>20</v>
+        <v>162</v>
       </c>
     </row>
     <row r="2" spans="1:27">
@@ -8466,7 +8531,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:AA2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="20"/>
   <sheetData>

--- a/DSlec/kakei2000.xlsx
+++ b/DSlec/kakei2000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yamamoto/R/bookdown/datalecture/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1B0E157F-F90A-2545-A0FD-4991723F4C18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDB81D0D-D776-694C-95F0-EB3A00296F88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7540" yWindow="3520" windowWidth="28300" windowHeight="17440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="163">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="169">
   <si>
     <t>2000年</t>
   </si>
@@ -512,6 +512,30 @@
   </si>
   <si>
     <t>FY2020</t>
+  </si>
+  <si>
+    <t>Category2</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>Category3</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>Category3J</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>Category2J</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>Category1J</t>
+    <phoneticPr fontId="18"/>
+  </si>
+  <si>
+    <t>Cateogry1</t>
+    <phoneticPr fontId="18"/>
   </si>
 </sst>
 </file>
@@ -1471,22 +1495,22 @@
   <sheetData>
     <row r="1" spans="1:27">
       <c r="A1" t="s">
-        <v>21</v>
+        <v>168</v>
       </c>
       <c r="B1" t="s">
-        <v>22</v>
+        <v>167</v>
       </c>
       <c r="C1" t="s">
-        <v>23</v>
+        <v>163</v>
       </c>
       <c r="D1" t="s">
-        <v>24</v>
+        <v>166</v>
       </c>
       <c r="E1" t="s">
-        <v>25</v>
+        <v>164</v>
       </c>
       <c r="F1" t="s">
-        <v>26</v>
+        <v>165</v>
       </c>
       <c r="G1" t="s">
         <v>142</v>
@@ -1554,13 +1578,13 @@
     </row>
     <row r="2" spans="1:27">
       <c r="A2">
-        <v>14</v>
-      </c>
-      <c r="B2">
-        <v>4</v>
-      </c>
-      <c r="C2" t="s">
+        <v>1</v>
+      </c>
+      <c r="B2" t="s">
         <v>29</v>
+      </c>
+      <c r="C2">
+        <v>10</v>
       </c>
       <c r="D2" t="s">
         <v>30</v>
@@ -1637,13 +1661,13 @@
     </row>
     <row r="3" spans="1:27">
       <c r="A3">
-        <v>15</v>
-      </c>
-      <c r="B3">
-        <v>4</v>
-      </c>
-      <c r="C3" t="s">
+        <v>1</v>
+      </c>
+      <c r="B3" t="s">
         <v>29</v>
+      </c>
+      <c r="C3">
+        <v>10</v>
       </c>
       <c r="D3" t="s">
         <v>30</v>
@@ -1720,13 +1744,13 @@
     </row>
     <row r="4" spans="1:27">
       <c r="A4">
-        <v>16</v>
-      </c>
-      <c r="B4">
-        <v>4</v>
-      </c>
-      <c r="C4" t="s">
+        <v>1</v>
+      </c>
+      <c r="B4" t="s">
         <v>29</v>
+      </c>
+      <c r="C4">
+        <v>10</v>
       </c>
       <c r="D4" t="s">
         <v>30</v>
@@ -1803,13 +1827,13 @@
     </row>
     <row r="5" spans="1:27">
       <c r="A5">
-        <v>17</v>
-      </c>
-      <c r="B5">
-        <v>4</v>
-      </c>
-      <c r="C5" t="s">
+        <v>1</v>
+      </c>
+      <c r="B5" t="s">
         <v>29</v>
+      </c>
+      <c r="C5">
+        <v>10</v>
       </c>
       <c r="D5" t="s">
         <v>30</v>
@@ -1886,13 +1910,13 @@
     </row>
     <row r="6" spans="1:27">
       <c r="A6">
-        <v>19</v>
-      </c>
-      <c r="B6">
-        <v>4</v>
-      </c>
-      <c r="C6" t="s">
+        <v>1</v>
+      </c>
+      <c r="B6" t="s">
         <v>29</v>
+      </c>
+      <c r="C6">
+        <v>11</v>
       </c>
       <c r="D6" t="s">
         <v>35</v>
@@ -1969,13 +1993,13 @@
     </row>
     <row r="7" spans="1:27">
       <c r="A7">
-        <v>20</v>
-      </c>
-      <c r="B7">
-        <v>4</v>
-      </c>
-      <c r="C7" t="s">
+        <v>1</v>
+      </c>
+      <c r="B7" t="s">
         <v>29</v>
+      </c>
+      <c r="C7">
+        <v>11</v>
       </c>
       <c r="D7" t="s">
         <v>35</v>
@@ -2052,13 +2076,13 @@
     </row>
     <row r="8" spans="1:27">
       <c r="A8">
-        <v>21</v>
-      </c>
-      <c r="B8">
-        <v>4</v>
-      </c>
-      <c r="C8" t="s">
+        <v>1</v>
+      </c>
+      <c r="B8" t="s">
         <v>29</v>
+      </c>
+      <c r="C8">
+        <v>11</v>
       </c>
       <c r="D8" t="s">
         <v>35</v>
@@ -2135,13 +2159,13 @@
     </row>
     <row r="9" spans="1:27">
       <c r="A9">
-        <v>22</v>
-      </c>
-      <c r="B9">
-        <v>4</v>
-      </c>
-      <c r="C9" t="s">
+        <v>1</v>
+      </c>
+      <c r="B9" t="s">
         <v>29</v>
+      </c>
+      <c r="C9">
+        <v>11</v>
       </c>
       <c r="D9" t="s">
         <v>35</v>
@@ -2218,13 +2242,13 @@
     </row>
     <row r="10" spans="1:27">
       <c r="A10">
-        <v>24</v>
-      </c>
-      <c r="B10">
-        <v>4</v>
-      </c>
-      <c r="C10" t="s">
+        <v>1</v>
+      </c>
+      <c r="B10" t="s">
         <v>29</v>
+      </c>
+      <c r="C10">
+        <v>12</v>
       </c>
       <c r="D10" t="s">
         <v>40</v>
@@ -2301,13 +2325,13 @@
     </row>
     <row r="11" spans="1:27">
       <c r="A11">
-        <v>25</v>
-      </c>
-      <c r="B11">
-        <v>4</v>
-      </c>
-      <c r="C11" t="s">
+        <v>1</v>
+      </c>
+      <c r="B11" t="s">
         <v>29</v>
+      </c>
+      <c r="C11">
+        <v>12</v>
       </c>
       <c r="D11" t="s">
         <v>40</v>
@@ -2384,13 +2408,13 @@
     </row>
     <row r="12" spans="1:27">
       <c r="A12">
-        <v>27</v>
-      </c>
-      <c r="B12">
-        <v>4</v>
-      </c>
-      <c r="C12" t="s">
+        <v>1</v>
+      </c>
+      <c r="B12" t="s">
         <v>29</v>
+      </c>
+      <c r="C12">
+        <v>13</v>
       </c>
       <c r="D12" t="s">
         <v>43</v>
@@ -2467,13 +2491,13 @@
     </row>
     <row r="13" spans="1:27">
       <c r="A13">
-        <v>28</v>
-      </c>
-      <c r="B13">
-        <v>4</v>
-      </c>
-      <c r="C13" t="s">
+        <v>1</v>
+      </c>
+      <c r="B13" t="s">
         <v>29</v>
+      </c>
+      <c r="C13">
+        <v>13</v>
       </c>
       <c r="D13" t="s">
         <v>43</v>
@@ -2550,13 +2574,13 @@
     </row>
     <row r="14" spans="1:27">
       <c r="A14">
+        <v>1</v>
+      </c>
+      <c r="B14" t="s">
         <v>29</v>
       </c>
-      <c r="B14">
-        <v>4</v>
-      </c>
-      <c r="C14" t="s">
-        <v>29</v>
+      <c r="C14">
+        <v>13</v>
       </c>
       <c r="D14" t="s">
         <v>43</v>
@@ -2633,13 +2657,13 @@
     </row>
     <row r="15" spans="1:27">
       <c r="A15">
-        <v>31</v>
-      </c>
-      <c r="B15">
-        <v>4</v>
-      </c>
-      <c r="C15" t="s">
+        <v>1</v>
+      </c>
+      <c r="B15" t="s">
         <v>29</v>
+      </c>
+      <c r="C15">
+        <v>14</v>
       </c>
       <c r="D15" t="s">
         <v>47</v>
@@ -2716,13 +2740,13 @@
     </row>
     <row r="16" spans="1:27">
       <c r="A16">
-        <v>32</v>
-      </c>
-      <c r="B16">
-        <v>4</v>
-      </c>
-      <c r="C16" t="s">
+        <v>1</v>
+      </c>
+      <c r="B16" t="s">
         <v>29</v>
+      </c>
+      <c r="C16">
+        <v>14</v>
       </c>
       <c r="D16" t="s">
         <v>47</v>
@@ -2799,13 +2823,13 @@
     </row>
     <row r="17" spans="1:27">
       <c r="A17">
-        <v>33</v>
-      </c>
-      <c r="B17">
-        <v>4</v>
-      </c>
-      <c r="C17" t="s">
+        <v>1</v>
+      </c>
+      <c r="B17" t="s">
         <v>29</v>
+      </c>
+      <c r="C17">
+        <v>14</v>
       </c>
       <c r="D17" t="s">
         <v>47</v>
@@ -2882,13 +2906,13 @@
     </row>
     <row r="18" spans="1:27">
       <c r="A18">
-        <v>34</v>
-      </c>
-      <c r="B18">
-        <v>4</v>
-      </c>
-      <c r="C18" t="s">
+        <v>1</v>
+      </c>
+      <c r="B18" t="s">
         <v>29</v>
+      </c>
+      <c r="C18">
+        <v>14</v>
       </c>
       <c r="D18" t="s">
         <v>47</v>
@@ -2965,13 +2989,13 @@
     </row>
     <row r="19" spans="1:27">
       <c r="A19">
-        <v>36</v>
-      </c>
-      <c r="B19">
-        <v>4</v>
-      </c>
-      <c r="C19" t="s">
+        <v>1</v>
+      </c>
+      <c r="B19" t="s">
         <v>29</v>
+      </c>
+      <c r="C19">
+        <v>15</v>
       </c>
       <c r="D19" t="s">
         <v>52</v>
@@ -3048,13 +3072,13 @@
     </row>
     <row r="20" spans="1:27">
       <c r="A20">
-        <v>37</v>
-      </c>
-      <c r="B20">
-        <v>4</v>
-      </c>
-      <c r="C20" t="s">
+        <v>1</v>
+      </c>
+      <c r="B20" t="s">
         <v>29</v>
+      </c>
+      <c r="C20">
+        <v>15</v>
       </c>
       <c r="D20" t="s">
         <v>52</v>
@@ -3131,13 +3155,13 @@
     </row>
     <row r="21" spans="1:27">
       <c r="A21">
-        <v>39</v>
-      </c>
-      <c r="B21">
-        <v>4</v>
-      </c>
-      <c r="C21" t="s">
+        <v>1</v>
+      </c>
+      <c r="B21" t="s">
         <v>29</v>
+      </c>
+      <c r="C21">
+        <v>16</v>
       </c>
       <c r="D21" t="s">
         <v>55</v>
@@ -3214,13 +3238,13 @@
     </row>
     <row r="22" spans="1:27">
       <c r="A22">
-        <v>40</v>
-      </c>
-      <c r="B22">
-        <v>4</v>
-      </c>
-      <c r="C22" t="s">
+        <v>1</v>
+      </c>
+      <c r="B22" t="s">
         <v>29</v>
+      </c>
+      <c r="C22">
+        <v>16</v>
       </c>
       <c r="D22" t="s">
         <v>55</v>
@@ -3297,13 +3321,13 @@
     </row>
     <row r="23" spans="1:27">
       <c r="A23">
-        <v>43</v>
-      </c>
-      <c r="B23">
-        <v>4</v>
-      </c>
-      <c r="C23" t="s">
+        <v>1</v>
+      </c>
+      <c r="B23" t="s">
         <v>29</v>
+      </c>
+      <c r="C23">
+        <v>17</v>
       </c>
       <c r="D23" t="s">
         <v>58</v>
@@ -3380,13 +3404,13 @@
     </row>
     <row r="24" spans="1:27">
       <c r="A24">
-        <v>44</v>
-      </c>
-      <c r="B24">
-        <v>4</v>
-      </c>
-      <c r="C24" t="s">
+        <v>1</v>
+      </c>
+      <c r="B24" t="s">
         <v>29</v>
+      </c>
+      <c r="C24">
+        <v>17</v>
       </c>
       <c r="D24" t="s">
         <v>58</v>
@@ -3463,13 +3487,13 @@
     </row>
     <row r="25" spans="1:27">
       <c r="A25">
-        <v>46</v>
-      </c>
-      <c r="B25">
-        <v>4</v>
-      </c>
-      <c r="C25" t="s">
+        <v>1</v>
+      </c>
+      <c r="B25" t="s">
         <v>29</v>
+      </c>
+      <c r="C25">
+        <v>18</v>
       </c>
       <c r="D25" t="s">
         <v>61</v>
@@ -3546,13 +3570,13 @@
     </row>
     <row r="26" spans="1:27">
       <c r="A26">
-        <v>47</v>
-      </c>
-      <c r="B26">
-        <v>4</v>
-      </c>
-      <c r="C26" t="s">
+        <v>1</v>
+      </c>
+      <c r="B26" t="s">
         <v>29</v>
+      </c>
+      <c r="C26">
+        <v>18</v>
       </c>
       <c r="D26" t="s">
         <v>61</v>
@@ -3629,13 +3653,13 @@
     </row>
     <row r="27" spans="1:27">
       <c r="A27">
-        <v>48</v>
-      </c>
-      <c r="B27">
-        <v>4</v>
-      </c>
-      <c r="C27" t="s">
+        <v>1</v>
+      </c>
+      <c r="B27" t="s">
         <v>29</v>
+      </c>
+      <c r="C27">
+        <v>18</v>
       </c>
       <c r="D27" t="s">
         <v>61</v>
@@ -3712,13 +3736,13 @@
     </row>
     <row r="28" spans="1:27">
       <c r="A28">
-        <v>51</v>
-      </c>
-      <c r="B28">
-        <v>4</v>
-      </c>
-      <c r="C28" t="s">
+        <v>1</v>
+      </c>
+      <c r="B28" t="s">
         <v>29</v>
+      </c>
+      <c r="C28">
+        <v>19</v>
       </c>
       <c r="D28" t="s">
         <v>65</v>
@@ -3795,13 +3819,13 @@
     </row>
     <row r="29" spans="1:27">
       <c r="A29">
-        <v>52</v>
-      </c>
-      <c r="B29">
-        <v>4</v>
-      </c>
-      <c r="C29" t="s">
+        <v>1</v>
+      </c>
+      <c r="B29" t="s">
         <v>29</v>
+      </c>
+      <c r="C29">
+        <v>19</v>
       </c>
       <c r="D29" t="s">
         <v>65</v>
@@ -3878,13 +3902,13 @@
     </row>
     <row r="30" spans="1:27">
       <c r="A30">
-        <v>56</v>
-      </c>
-      <c r="B30">
-        <v>4</v>
-      </c>
-      <c r="C30" t="s">
+        <v>2</v>
+      </c>
+      <c r="B30" t="s">
         <v>68</v>
+      </c>
+      <c r="C30">
+        <v>20</v>
       </c>
       <c r="D30" t="s">
         <v>69</v>
@@ -3961,13 +3985,13 @@
     </row>
     <row r="31" spans="1:27">
       <c r="A31">
-        <v>57</v>
-      </c>
-      <c r="B31">
-        <v>4</v>
-      </c>
-      <c r="C31" t="s">
+        <v>2</v>
+      </c>
+      <c r="B31" t="s">
         <v>68</v>
+      </c>
+      <c r="C31">
+        <v>20</v>
       </c>
       <c r="D31" t="s">
         <v>69</v>
@@ -4044,13 +4068,13 @@
     </row>
     <row r="32" spans="1:27">
       <c r="A32">
-        <v>59</v>
-      </c>
-      <c r="B32">
         <v>3</v>
       </c>
-      <c r="C32" t="s">
+      <c r="B32" t="s">
         <v>72</v>
+      </c>
+      <c r="C32">
+        <v>30</v>
       </c>
       <c r="D32" t="s">
         <v>73</v>
@@ -4127,13 +4151,13 @@
     </row>
     <row r="33" spans="1:27">
       <c r="A33">
-        <v>60</v>
-      </c>
-      <c r="B33">
         <v>3</v>
       </c>
-      <c r="C33" t="s">
+      <c r="B33" t="s">
         <v>72</v>
+      </c>
+      <c r="C33">
+        <v>31</v>
       </c>
       <c r="D33" t="s">
         <v>74</v>
@@ -4210,13 +4234,13 @@
     </row>
     <row r="34" spans="1:27">
       <c r="A34">
-        <v>61</v>
-      </c>
-      <c r="B34">
         <v>3</v>
       </c>
-      <c r="C34" t="s">
+      <c r="B34" t="s">
         <v>72</v>
+      </c>
+      <c r="C34">
+        <v>31</v>
       </c>
       <c r="D34" t="s">
         <v>75</v>
@@ -4293,13 +4317,13 @@
     </row>
     <row r="35" spans="1:27">
       <c r="A35">
-        <v>62</v>
-      </c>
-      <c r="B35">
         <v>3</v>
       </c>
-      <c r="C35" t="s">
+      <c r="B35" t="s">
         <v>72</v>
+      </c>
+      <c r="C35">
+        <v>33</v>
       </c>
       <c r="D35" t="s">
         <v>76</v>
@@ -4376,13 +4400,13 @@
     </row>
     <row r="36" spans="1:27">
       <c r="A36">
-        <v>65</v>
-      </c>
-      <c r="B36">
         <v>4</v>
       </c>
-      <c r="C36" t="s">
+      <c r="B36" t="s">
         <v>77</v>
+      </c>
+      <c r="C36">
+        <v>40</v>
       </c>
       <c r="D36" t="s">
         <v>78</v>
@@ -4459,13 +4483,13 @@
     </row>
     <row r="37" spans="1:27">
       <c r="A37">
-        <v>66</v>
-      </c>
-      <c r="B37">
         <v>4</v>
       </c>
-      <c r="C37" t="s">
+      <c r="B37" t="s">
         <v>77</v>
+      </c>
+      <c r="C37">
+        <v>40</v>
       </c>
       <c r="D37" t="s">
         <v>78</v>
@@ -4542,13 +4566,13 @@
     </row>
     <row r="38" spans="1:27">
       <c r="A38">
-        <v>67</v>
-      </c>
-      <c r="B38">
         <v>4</v>
       </c>
-      <c r="C38" t="s">
+      <c r="B38" t="s">
         <v>77</v>
+      </c>
+      <c r="C38">
+        <v>40</v>
       </c>
       <c r="D38" t="s">
         <v>78</v>
@@ -4625,13 +4649,13 @@
     </row>
     <row r="39" spans="1:27">
       <c r="A39">
-        <v>68</v>
-      </c>
-      <c r="B39">
-        <v>3</v>
-      </c>
-      <c r="C39" t="s">
+        <v>4</v>
+      </c>
+      <c r="B39" t="s">
         <v>77</v>
+      </c>
+      <c r="C39">
+        <v>41</v>
       </c>
       <c r="D39" t="s">
         <v>82</v>
@@ -4708,13 +4732,13 @@
     </row>
     <row r="40" spans="1:27">
       <c r="A40">
-        <v>69</v>
-      </c>
-      <c r="B40">
-        <v>3</v>
-      </c>
-      <c r="C40" t="s">
+        <v>4</v>
+      </c>
+      <c r="B40" t="s">
         <v>77</v>
+      </c>
+      <c r="C40">
+        <v>42</v>
       </c>
       <c r="D40" t="s">
         <v>83</v>
@@ -4791,13 +4815,13 @@
     </row>
     <row r="41" spans="1:27">
       <c r="A41">
-        <v>70</v>
-      </c>
-      <c r="B41">
-        <v>3</v>
-      </c>
-      <c r="C41" t="s">
+        <v>4</v>
+      </c>
+      <c r="B41" t="s">
         <v>77</v>
+      </c>
+      <c r="C41">
+        <v>43</v>
       </c>
       <c r="D41" t="s">
         <v>84</v>
@@ -4874,13 +4898,13 @@
     </row>
     <row r="42" spans="1:27">
       <c r="A42">
-        <v>71</v>
-      </c>
-      <c r="B42">
-        <v>3</v>
-      </c>
-      <c r="C42" t="s">
+        <v>4</v>
+      </c>
+      <c r="B42" t="s">
         <v>77</v>
+      </c>
+      <c r="C42">
+        <v>44</v>
       </c>
       <c r="D42" t="s">
         <v>85</v>
@@ -4957,13 +4981,13 @@
     </row>
     <row r="43" spans="1:27">
       <c r="A43">
-        <v>72</v>
-      </c>
-      <c r="B43">
-        <v>3</v>
-      </c>
-      <c r="C43" t="s">
+        <v>4</v>
+      </c>
+      <c r="B43" t="s">
         <v>77</v>
+      </c>
+      <c r="C43">
+        <v>45</v>
       </c>
       <c r="D43" t="s">
         <v>86</v>
@@ -5040,13 +5064,13 @@
     </row>
     <row r="44" spans="1:27">
       <c r="A44">
-        <v>74</v>
-      </c>
-      <c r="B44">
-        <v>3</v>
-      </c>
-      <c r="C44" t="s">
+        <v>5</v>
+      </c>
+      <c r="B44" t="s">
         <v>87</v>
+      </c>
+      <c r="C44">
+        <v>50</v>
       </c>
       <c r="D44" t="s">
         <v>88</v>
@@ -5123,13 +5147,13 @@
     </row>
     <row r="45" spans="1:27">
       <c r="A45">
-        <v>76</v>
-      </c>
-      <c r="B45">
-        <v>4</v>
-      </c>
-      <c r="C45" t="s">
+        <v>5</v>
+      </c>
+      <c r="B45" t="s">
         <v>87</v>
+      </c>
+      <c r="C45">
+        <v>51</v>
       </c>
       <c r="D45" t="s">
         <v>89</v>
@@ -5206,13 +5230,13 @@
     </row>
     <row r="46" spans="1:27">
       <c r="A46">
-        <v>77</v>
-      </c>
-      <c r="B46">
-        <v>4</v>
-      </c>
-      <c r="C46" t="s">
+        <v>5</v>
+      </c>
+      <c r="B46" t="s">
         <v>87</v>
+      </c>
+      <c r="C46">
+        <v>51</v>
       </c>
       <c r="D46" t="s">
         <v>89</v>
@@ -5289,13 +5313,13 @@
     </row>
     <row r="47" spans="1:27">
       <c r="A47">
-        <v>78</v>
-      </c>
-      <c r="B47">
-        <v>4</v>
-      </c>
-      <c r="C47" t="s">
+        <v>5</v>
+      </c>
+      <c r="B47" t="s">
         <v>87</v>
+      </c>
+      <c r="C47">
+        <v>51</v>
       </c>
       <c r="D47" t="s">
         <v>89</v>
@@ -5372,13 +5396,13 @@
     </row>
     <row r="48" spans="1:27">
       <c r="A48">
-        <v>80</v>
-      </c>
-      <c r="B48">
-        <v>4</v>
-      </c>
-      <c r="C48" t="s">
+        <v>5</v>
+      </c>
+      <c r="B48" t="s">
         <v>87</v>
+      </c>
+      <c r="C48">
+        <v>52</v>
       </c>
       <c r="D48" t="s">
         <v>93</v>
@@ -5455,13 +5479,13 @@
     </row>
     <row r="49" spans="1:27">
       <c r="A49">
-        <v>81</v>
-      </c>
-      <c r="B49">
-        <v>4</v>
-      </c>
-      <c r="C49" t="s">
+        <v>5</v>
+      </c>
+      <c r="B49" t="s">
         <v>87</v>
+      </c>
+      <c r="C49">
+        <v>52</v>
       </c>
       <c r="D49" t="s">
         <v>93</v>
@@ -5538,13 +5562,13 @@
     </row>
     <row r="50" spans="1:27">
       <c r="A50">
-        <v>82</v>
-      </c>
-      <c r="B50">
-        <v>4</v>
-      </c>
-      <c r="C50" t="s">
+        <v>5</v>
+      </c>
+      <c r="B50" t="s">
         <v>87</v>
+      </c>
+      <c r="C50">
+        <v>52</v>
       </c>
       <c r="D50" t="s">
         <v>93</v>
@@ -5621,13 +5645,13 @@
     </row>
     <row r="51" spans="1:27">
       <c r="A51">
-        <v>84</v>
-      </c>
-      <c r="B51">
-        <v>4</v>
-      </c>
-      <c r="C51" t="s">
+        <v>5</v>
+      </c>
+      <c r="B51" t="s">
         <v>87</v>
+      </c>
+      <c r="C51">
+        <v>53</v>
       </c>
       <c r="D51" t="s">
         <v>97</v>
@@ -5704,13 +5728,13 @@
     </row>
     <row r="52" spans="1:27">
       <c r="A52">
-        <v>85</v>
-      </c>
-      <c r="B52">
-        <v>4</v>
-      </c>
-      <c r="C52" t="s">
+        <v>5</v>
+      </c>
+      <c r="B52" t="s">
         <v>87</v>
+      </c>
+      <c r="C52">
+        <v>53</v>
       </c>
       <c r="D52" t="s">
         <v>97</v>
@@ -5787,13 +5811,13 @@
     </row>
     <row r="53" spans="1:27">
       <c r="A53">
-        <v>86</v>
-      </c>
-      <c r="B53">
-        <v>4</v>
-      </c>
-      <c r="C53" t="s">
+        <v>5</v>
+      </c>
+      <c r="B53" t="s">
         <v>87</v>
+      </c>
+      <c r="C53">
+        <v>53</v>
       </c>
       <c r="D53" t="s">
         <v>97</v>
@@ -5870,13 +5894,13 @@
     </row>
     <row r="54" spans="1:27">
       <c r="A54">
+        <v>5</v>
+      </c>
+      <c r="B54" t="s">
         <v>87</v>
       </c>
-      <c r="B54">
-        <v>3</v>
-      </c>
-      <c r="C54" t="s">
-        <v>87</v>
+      <c r="C54">
+        <v>54</v>
       </c>
       <c r="D54" t="s">
         <v>101</v>
@@ -5953,13 +5977,13 @@
     </row>
     <row r="55" spans="1:27">
       <c r="A55">
-        <v>88</v>
-      </c>
-      <c r="B55">
-        <v>3</v>
-      </c>
-      <c r="C55" t="s">
+        <v>5</v>
+      </c>
+      <c r="B55" t="s">
         <v>87</v>
+      </c>
+      <c r="C55">
+        <v>55</v>
       </c>
       <c r="D55" t="s">
         <v>102</v>
@@ -6036,13 +6060,13 @@
     </row>
     <row r="56" spans="1:27">
       <c r="A56">
-        <v>89</v>
-      </c>
-      <c r="B56">
-        <v>3</v>
-      </c>
-      <c r="C56" t="s">
+        <v>5</v>
+      </c>
+      <c r="B56" t="s">
         <v>87</v>
+      </c>
+      <c r="C56">
+        <v>56</v>
       </c>
       <c r="D56" t="s">
         <v>103</v>
@@ -6119,13 +6143,13 @@
     </row>
     <row r="57" spans="1:27">
       <c r="A57">
-        <v>90</v>
-      </c>
-      <c r="B57">
-        <v>3</v>
-      </c>
-      <c r="C57" t="s">
+        <v>5</v>
+      </c>
+      <c r="B57" t="s">
         <v>87</v>
+      </c>
+      <c r="C57">
+        <v>57</v>
       </c>
       <c r="D57" t="s">
         <v>104</v>
@@ -6202,13 +6226,13 @@
     </row>
     <row r="58" spans="1:27">
       <c r="A58">
-        <v>92</v>
-      </c>
-      <c r="B58">
-        <v>3</v>
-      </c>
-      <c r="C58" t="s">
+        <v>6</v>
+      </c>
+      <c r="B58" t="s">
         <v>105</v>
+      </c>
+      <c r="C58">
+        <v>60</v>
       </c>
       <c r="D58" t="s">
         <v>106</v>
@@ -6285,13 +6309,13 @@
     </row>
     <row r="59" spans="1:27">
       <c r="A59">
-        <v>93</v>
-      </c>
-      <c r="B59">
-        <v>3</v>
-      </c>
-      <c r="C59" t="s">
+        <v>6</v>
+      </c>
+      <c r="B59" t="s">
         <v>105</v>
+      </c>
+      <c r="C59">
+        <v>61</v>
       </c>
       <c r="D59" t="s">
         <v>107</v>
@@ -6368,13 +6392,13 @@
     </row>
     <row r="60" spans="1:27">
       <c r="A60">
-        <v>94</v>
-      </c>
-      <c r="B60">
-        <v>3</v>
-      </c>
-      <c r="C60" t="s">
+        <v>6</v>
+      </c>
+      <c r="B60" t="s">
         <v>105</v>
+      </c>
+      <c r="C60">
+        <v>62</v>
       </c>
       <c r="D60" t="s">
         <v>108</v>
@@ -6451,13 +6475,13 @@
     </row>
     <row r="61" spans="1:27">
       <c r="A61">
-        <v>95</v>
-      </c>
-      <c r="B61">
-        <v>3</v>
-      </c>
-      <c r="C61" t="s">
+        <v>6</v>
+      </c>
+      <c r="B61" t="s">
         <v>105</v>
+      </c>
+      <c r="C61">
+        <v>63</v>
       </c>
       <c r="D61" t="s">
         <v>109</v>
@@ -6534,13 +6558,13 @@
     </row>
     <row r="62" spans="1:27">
       <c r="A62">
-        <v>97</v>
-      </c>
-      <c r="B62">
-        <v>3</v>
-      </c>
-      <c r="C62" t="s">
+        <v>7</v>
+      </c>
+      <c r="B62" t="s">
         <v>110</v>
+      </c>
+      <c r="C62">
+        <v>70</v>
       </c>
       <c r="D62" t="s">
         <v>111</v>
@@ -6617,13 +6641,13 @@
     </row>
     <row r="63" spans="1:27">
       <c r="A63">
-        <v>99</v>
-      </c>
-      <c r="B63">
-        <v>4</v>
-      </c>
-      <c r="C63" t="s">
+        <v>7</v>
+      </c>
+      <c r="B63" t="s">
         <v>110</v>
+      </c>
+      <c r="C63">
+        <v>71</v>
       </c>
       <c r="D63" t="s">
         <v>112</v>
@@ -6700,13 +6724,13 @@
     </row>
     <row r="64" spans="1:27">
       <c r="A64">
-        <v>100</v>
-      </c>
-      <c r="B64">
-        <v>4</v>
-      </c>
-      <c r="C64" t="s">
+        <v>7</v>
+      </c>
+      <c r="B64" t="s">
         <v>110</v>
+      </c>
+      <c r="C64">
+        <v>71</v>
       </c>
       <c r="D64" t="s">
         <v>112</v>
@@ -6783,13 +6807,13 @@
     </row>
     <row r="65" spans="1:27">
       <c r="A65">
-        <v>101</v>
-      </c>
-      <c r="B65">
-        <v>4</v>
-      </c>
-      <c r="C65" t="s">
+        <v>7</v>
+      </c>
+      <c r="B65" t="s">
         <v>110</v>
+      </c>
+      <c r="C65">
+        <v>71</v>
       </c>
       <c r="D65" t="s">
         <v>112</v>
@@ -6866,13 +6890,13 @@
     </row>
     <row r="66" spans="1:27">
       <c r="A66">
-        <v>102</v>
-      </c>
-      <c r="B66">
-        <v>3</v>
-      </c>
-      <c r="C66" t="s">
+        <v>7</v>
+      </c>
+      <c r="B66" t="s">
         <v>110</v>
+      </c>
+      <c r="C66">
+        <v>72</v>
       </c>
       <c r="D66" t="s">
         <v>116</v>
@@ -6949,13 +6973,13 @@
     </row>
     <row r="67" spans="1:27">
       <c r="A67">
-        <v>104</v>
-      </c>
-      <c r="B67">
-        <v>3</v>
-      </c>
-      <c r="C67" t="s">
+        <v>8</v>
+      </c>
+      <c r="B67" t="s">
         <v>117</v>
+      </c>
+      <c r="C67">
+        <v>80</v>
       </c>
       <c r="D67" t="s">
         <v>118</v>
@@ -7032,13 +7056,13 @@
     </row>
     <row r="68" spans="1:27">
       <c r="A68">
-        <v>105</v>
-      </c>
-      <c r="B68">
-        <v>3</v>
-      </c>
-      <c r="C68" t="s">
+        <v>8</v>
+      </c>
+      <c r="B68" t="s">
         <v>117</v>
+      </c>
+      <c r="C68">
+        <v>81</v>
       </c>
       <c r="D68" t="s">
         <v>119</v>
@@ -7115,13 +7139,13 @@
     </row>
     <row r="69" spans="1:27">
       <c r="A69">
-        <v>106</v>
-      </c>
-      <c r="B69">
-        <v>3</v>
-      </c>
-      <c r="C69" t="s">
+        <v>8</v>
+      </c>
+      <c r="B69" t="s">
         <v>117</v>
+      </c>
+      <c r="C69">
+        <v>82</v>
       </c>
       <c r="D69" t="s">
         <v>120</v>
@@ -7198,13 +7222,13 @@
     </row>
     <row r="70" spans="1:27">
       <c r="A70">
-        <v>108</v>
-      </c>
-      <c r="B70">
-        <v>3</v>
-      </c>
-      <c r="C70" t="s">
+        <v>9</v>
+      </c>
+      <c r="B70" t="s">
         <v>121</v>
+      </c>
+      <c r="C70">
+        <v>90</v>
       </c>
       <c r="D70" t="s">
         <v>122</v>
@@ -7281,13 +7305,13 @@
     </row>
     <row r="71" spans="1:27">
       <c r="A71">
-        <v>109</v>
-      </c>
-      <c r="B71">
-        <v>3</v>
-      </c>
-      <c r="C71" t="s">
+        <v>9</v>
+      </c>
+      <c r="B71" t="s">
         <v>121</v>
+      </c>
+      <c r="C71">
+        <v>91</v>
       </c>
       <c r="D71" t="s">
         <v>123</v>
@@ -7364,13 +7388,13 @@
     </row>
     <row r="72" spans="1:27">
       <c r="A72">
-        <v>110</v>
-      </c>
-      <c r="B72">
-        <v>3</v>
-      </c>
-      <c r="C72" t="s">
+        <v>9</v>
+      </c>
+      <c r="B72" t="s">
         <v>121</v>
+      </c>
+      <c r="C72">
+        <v>92</v>
       </c>
       <c r="D72" t="s">
         <v>124</v>
@@ -7447,13 +7471,13 @@
     </row>
     <row r="73" spans="1:27">
       <c r="A73">
-        <v>112</v>
-      </c>
-      <c r="B73">
-        <v>4</v>
-      </c>
-      <c r="C73" t="s">
+        <v>9</v>
+      </c>
+      <c r="B73" t="s">
         <v>121</v>
+      </c>
+      <c r="C73">
+        <v>93</v>
       </c>
       <c r="D73" t="s">
         <v>125</v>
@@ -7530,13 +7554,13 @@
     </row>
     <row r="74" spans="1:27">
       <c r="A74">
-        <v>113</v>
-      </c>
-      <c r="B74">
-        <v>4</v>
-      </c>
-      <c r="C74" t="s">
+        <v>9</v>
+      </c>
+      <c r="B74" t="s">
         <v>121</v>
+      </c>
+      <c r="C74">
+        <v>93</v>
       </c>
       <c r="D74" t="s">
         <v>125</v>
@@ -7613,13 +7637,13 @@
     </row>
     <row r="75" spans="1:27">
       <c r="A75">
-        <v>114</v>
-      </c>
-      <c r="B75">
-        <v>4</v>
-      </c>
-      <c r="C75" t="s">
+        <v>9</v>
+      </c>
+      <c r="B75" t="s">
         <v>121</v>
+      </c>
+      <c r="C75">
+        <v>93</v>
       </c>
       <c r="D75" t="s">
         <v>125</v>
@@ -7696,13 +7720,13 @@
     </row>
     <row r="76" spans="1:27">
       <c r="A76">
-        <v>115</v>
-      </c>
-      <c r="B76">
-        <v>4</v>
-      </c>
-      <c r="C76" t="s">
+        <v>9</v>
+      </c>
+      <c r="B76" t="s">
         <v>121</v>
+      </c>
+      <c r="C76">
+        <v>93</v>
       </c>
       <c r="D76" t="s">
         <v>125</v>
@@ -7779,13 +7803,13 @@
     </row>
     <row r="77" spans="1:27">
       <c r="A77">
-        <v>118</v>
-      </c>
-      <c r="B77">
-        <v>4</v>
-      </c>
-      <c r="C77" t="s">
+        <v>10</v>
+      </c>
+      <c r="B77" t="s">
         <v>130</v>
+      </c>
+      <c r="C77">
+        <v>100</v>
       </c>
       <c r="D77" t="s">
         <v>131</v>
@@ -7862,13 +7886,13 @@
     </row>
     <row r="78" spans="1:27">
       <c r="A78">
-        <v>119</v>
-      </c>
-      <c r="B78">
-        <v>4</v>
-      </c>
-      <c r="C78" t="s">
+        <v>10</v>
+      </c>
+      <c r="B78" t="s">
         <v>130</v>
+      </c>
+      <c r="C78">
+        <v>100</v>
       </c>
       <c r="D78" t="s">
         <v>131</v>
@@ -7945,13 +7969,13 @@
     </row>
     <row r="79" spans="1:27">
       <c r="A79">
-        <v>120</v>
-      </c>
-      <c r="B79">
-        <v>4</v>
-      </c>
-      <c r="C79" t="s">
+        <v>10</v>
+      </c>
+      <c r="B79" t="s">
         <v>130</v>
+      </c>
+      <c r="C79">
+        <v>100</v>
       </c>
       <c r="D79" t="s">
         <v>131</v>
@@ -8028,13 +8052,13 @@
     </row>
     <row r="80" spans="1:27">
       <c r="A80">
-        <v>121</v>
-      </c>
-      <c r="B80">
-        <v>4</v>
-      </c>
-      <c r="C80" t="s">
+        <v>10</v>
+      </c>
+      <c r="B80" t="s">
         <v>130</v>
+      </c>
+      <c r="C80">
+        <v>100</v>
       </c>
       <c r="D80" t="s">
         <v>131</v>
@@ -8111,13 +8135,13 @@
     </row>
     <row r="81" spans="1:27">
       <c r="A81">
-        <v>122</v>
-      </c>
-      <c r="B81">
-        <v>4</v>
-      </c>
-      <c r="C81" t="s">
+        <v>10</v>
+      </c>
+      <c r="B81" t="s">
         <v>130</v>
+      </c>
+      <c r="C81">
+        <v>100</v>
       </c>
       <c r="D81" t="s">
         <v>131</v>
@@ -8194,13 +8218,13 @@
     </row>
     <row r="82" spans="1:27">
       <c r="A82">
-        <v>123</v>
-      </c>
-      <c r="B82">
-        <v>3</v>
-      </c>
-      <c r="C82" t="s">
+        <v>10</v>
+      </c>
+      <c r="B82" t="s">
         <v>130</v>
+      </c>
+      <c r="C82">
+        <v>101</v>
       </c>
       <c r="D82" t="s">
         <v>137</v>
@@ -8277,13 +8301,13 @@
     </row>
     <row r="83" spans="1:27">
       <c r="A83">
-        <v>125</v>
-      </c>
-      <c r="B83">
-        <v>4</v>
-      </c>
-      <c r="C83" t="s">
+        <v>10</v>
+      </c>
+      <c r="B83" t="s">
         <v>130</v>
+      </c>
+      <c r="C83">
+        <v>102</v>
       </c>
       <c r="D83" t="s">
         <v>138</v>
@@ -8360,13 +8384,13 @@
     </row>
     <row r="84" spans="1:27">
       <c r="A84">
-        <v>126</v>
-      </c>
-      <c r="B84">
-        <v>4</v>
-      </c>
-      <c r="C84" t="s">
+        <v>10</v>
+      </c>
+      <c r="B84" t="s">
         <v>130</v>
+      </c>
+      <c r="C84">
+        <v>102</v>
       </c>
       <c r="D84" t="s">
         <v>138</v>
@@ -8443,13 +8467,13 @@
     </row>
     <row r="85" spans="1:27">
       <c r="A85">
-        <v>127</v>
-      </c>
-      <c r="B85">
-        <v>3</v>
-      </c>
-      <c r="C85" t="s">
+        <v>10</v>
+      </c>
+      <c r="B85" t="s">
         <v>130</v>
+      </c>
+      <c r="C85">
+        <v>103</v>
       </c>
       <c r="D85" t="s">
         <v>141</v>

--- a/DSlec/kakei2000.xlsx
+++ b/DSlec/kakei2000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yamamoto/R/bookdown/datalecture/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDB81D0D-D776-694C-95F0-EB3A00296F88}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{763F45D2-A805-954B-A54E-FF1D06FE47F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7540" yWindow="3520" windowWidth="28300" windowHeight="17440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -534,7 +534,7 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>Cateogry1</t>
+    <t>Cateogory1</t>
     <phoneticPr fontId="18"/>
   </si>
 </sst>

--- a/DSlec/kakei2000.xlsx
+++ b/DSlec/kakei2000.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/yamamoto/R/bookdown/datalecture/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{763F45D2-A805-954B-A54E-FF1D06FE47F4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AEC31F4-450B-614C-A6DD-95668B51D81A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="7540" yWindow="3520" windowWidth="28300" windowHeight="17440" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -534,7 +534,7 @@
     <phoneticPr fontId="18"/>
   </si>
   <si>
-    <t>Cateogory1</t>
+    <t>Category1</t>
     <phoneticPr fontId="18"/>
   </si>
 </sst>
